--- a/healthcare_surveys/048_healthcare_team_collaboration_workshop_evaluation--healthcare_surveys.xlsx
+++ b/healthcare_surveys/048_healthcare_team_collaboration_workshop_evaluation--healthcare_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -715,12 +715,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -748,12 +748,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'effective'}</t>
+          <t>effective</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Effective'}</t>
+          <t>Effective</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'ineffective'}</t>
+          <t>ineffective</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Ineffective'}</t>
+          <t>Ineffective</t>
         </is>
       </c>
     </row>
@@ -782,12 +782,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_effective'}</t>
+          <t>somewhat_effective</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Effective'}</t>
+          <t>Somewhat Effective</t>
         </is>
       </c>
     </row>
@@ -799,12 +799,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -816,29 +816,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_ineffective'}</t>
+          <t>somewhat_ineffective</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Ineffective'}</t>
+          <t>Somewhat Ineffective</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>team_collaboration_choices</t>
+          <t>workshop_participants_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'ineffective'}</t>
+          <t>effective</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Ineffective'}</t>
+          <t>Effective</t>
         </is>
       </c>
     </row>
@@ -850,12 +850,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'effective'}</t>
+          <t>ineffective</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Effective'}</t>
+          <t>Ineffective</t>
         </is>
       </c>
     </row>
@@ -867,12 +867,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'ineffective'}</t>
+          <t>somewhat_effective</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Ineffective'}</t>
+          <t>Somewhat Effective</t>
         </is>
       </c>
     </row>
@@ -884,12 +884,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_effective'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Effective'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -901,80 +901,46 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>somewhat_ineffective</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Somewhat Ineffective</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>workshop_participants_choices</t>
+          <t>improvement_ideas_implement_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_ineffective'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Ineffective'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>workshop_participants_choices</t>
+          <t>improvement_ideas_implement_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'ineffective'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Ineffective'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>improvement_ideas_implement_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>{'label':_true}</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>{'label': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>improvement_ideas_implement_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>{'label':_false}</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
